--- a/data/_general_data/diets/all_feeds.xlsx
+++ b/data/_general_data/diets/all_feeds.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\local_to_global_mariculture_modelling\data\_general_data\diets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D1BEB5-488C-4871-9A1E-B0076EF06FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5880B23D-73AB-4B48-BD58-74E31DC65400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28548" yWindow="540" windowWidth="12456" windowHeight="15132" xr2:uid="{A3945701-1F25-4092-97C8-50D4B2B937C4}"/>
+    <workbookView xWindow="22404" yWindow="0" windowWidth="17040" windowHeight="16656" xr2:uid="{A3945701-1F25-4092-97C8-50D4B2B937C4}"/>
   </bookViews>
   <sheets>
     <sheet name="all_feeds" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all_feeds!$A$1:$G$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all_feeds!$A$1:$J$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2078,11 +2078,7 @@
       <c r="G39" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G39" xr:uid="{76559CA1-42BE-4BD5-A831-409A491DC0E7}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G39">
-      <sortCondition ref="A1:A39"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:J39" xr:uid="{76559CA1-42BE-4BD5-A831-409A491DC0E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
